--- a/МО 19.10.2026/Списки МО итог (ред. 19.10.2026).xlsx
+++ b/МО 19.10.2026/Списки МО итог (ред. 19.10.2026).xlsx
@@ -41,7 +41,7 @@
     <t xml:space="preserve">Сводка по площадкам: медицинские осмотры и психиатрическое освидетельствование, 2026 год</t>
   </si>
   <si>
-    <t xml:space="preserve">Источник: «Учёт медосмотров» на 15.10.2026; статусы на 16.10.2026. Графы C–H считаются формулами по листам «Периодический 2026» и «Психиатрическое».</t>
+    <t xml:space="preserve">Источник: «Учёт медосмотров» на 19.10.2026; статусы на 19.10.2026. Графы C–H считаются формулами по листам «Периодический 2026» и «Психиатрическое».</t>
   </si>
   <si>
     <t xml:space="preserve">Площадка</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">Список работников, подлежащих периодическому медицинскому осмотру в 2026 году</t>
   </si>
   <si>
-    <t xml:space="preserve">Источник: «Учёт медосмотров» на 15.10.2026. Всего: 331 чел.</t>
+    <t xml:space="preserve">Источник: «Учёт медосмотров» на 19.10.2026. Всего: 331 чел.</t>
   </si>
   <si>
     <t xml:space="preserve">№</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">Дата периодич. осмотра (план)</t>
   </si>
   <si>
-    <t xml:space="preserve">Статус на 16.10.2026</t>
+    <t xml:space="preserve">Статус на 19.10.2026</t>
   </si>
   <si>
     <t xml:space="preserve">Алфимов Дмитрий Юрьевич</t>
@@ -419,75 +419,75 @@
     <t xml:space="preserve">Михайлов Никита Алексеевич</t>
   </si>
   <si>
+    <t xml:space="preserve">Мысовских Александр Александрович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Петренко Дмитрий Сергеевич</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Попов Андрей Михайлович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Попов Олег Владимирович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Попов Роман Юрьевич</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Потамошнев Константин Сергеевич</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Роговский Александр Викторович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Русанов Александр Евгеньевич</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рябинин Александр Анатольевич</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Самодуров Алексей Юрьевич</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сидоренко Сергей Владимирович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сорокин Олег Владимирович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Студеникин Михаил Вячеславович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тимошкин Сергей Александрович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шпилев Михаил Сергеевич</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тимофеева Галина Петровна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Технический работник</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Административно-хозяйственный отдел Ж</t>
+  </si>
+  <si>
+    <t xml:space="preserve">п.1.48, п.4.3.1, п.4.4, п.5.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Андреев Алексей Владимирович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обособленное подразделение Казань</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аюпов Булат Фаилевич</t>
+  </si>
+  <si>
     <t xml:space="preserve">Предстоит</t>
   </si>
   <si>
-    <t xml:space="preserve">Мысовских Александр Александрович</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Петренко Дмитрий Сергеевич</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Попов Андрей Михайлович</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Попов Олег Владимирович</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Попов Роман Юрьевич</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Потамошнев Константин Сергеевич</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Роговский Александр Викторович</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Русанов Александр Евгеньевич</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Рябинин Александр Анатольевич</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Самодуров Алексей Юрьевич</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сидоренко Сергей Владимирович</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сорокин Олег Владимирович</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Студеникин Михаил Вячеславович</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тимошкин Сергей Александрович</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Шпилев Михаил Сергеевич</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тимофеева Галина Петровна</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Технический работник</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Административно-хозяйственный отдел Ж</t>
-  </si>
-  <si>
-    <t xml:space="preserve">п.1.48, п.4.3.1, п.4.4, п.5.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Андреев Алексей Владимирович</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Обособленное подразделение Казань</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Аюпов Булат Фаилевич</t>
-  </si>
-  <si>
     <t xml:space="preserve">Булатова Лия Рустэмовна</t>
   </si>
   <si>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">Список работников, подлежащих психиатрическому освидетельствованию (графа «Подлежит» = «Да»)</t>
   </si>
   <si>
-    <t xml:space="preserve">Источник: «Учёт медосмотров» на 15.10.2026. Всего: 59 чел.</t>
+    <t xml:space="preserve">Источник: «Учёт медосмотров» на 19.10.2026. Всего: 59 чел.</t>
   </si>
   <si>
     <t xml:space="preserve">Основание (Перечень)</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">Площадка «Машково»: медицинские осмотры и психиатрическое освидетельствование, 2026 год</t>
   </si>
   <si>
-    <t xml:space="preserve">Источник: «Учёт медосмотров» на 15.10.2026; статусы на 16.10.2026.</t>
+    <t xml:space="preserve">Источник: «Учёт медосмотров» на 19.10.2026; статусы на 19.10.2026.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Периодический медицинский осмотр в 2026 году — 165 чел.</t>
@@ -2408,11 +2408,11 @@
       </c>
       <c r="E7" s="6" t="n">
         <f aca="false">COUNTIFS('Периодический 2026'!$B$5:$B$1000,A7,'Периодический 2026'!$J$5:$J$1000,"Просрочен")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7" s="6" t="n">
         <f aca="false">COUNTIFS('Периодический 2026'!$B$5:$B$1000,A7,'Периодический 2026'!$J$5:$J$1000,"Предстоит")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="6" t="n">
         <f aca="false">COUNTIFS('Периодический 2026'!$B$5:$B$1000,A7,'Периодический 2026'!$G$5:$G$1000,"&gt;="&amp;DATE(2026,1,1))</f>
@@ -2601,11 +2601,11 @@
       </c>
       <c r="E13" s="8" t="n">
         <f aca="false">SUM(E5:E12)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F13" s="8" t="n">
         <f aca="false">SUM(F5:F12)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G13" s="8" t="n">
         <f aca="false">SUM(G5:G12)</f>
@@ -2731,7 +2731,7 @@
         <v>423</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>43283</v>
@@ -2756,7 +2756,7 @@
         <v>423</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>46065</v>
@@ -2781,7 +2781,7 @@
         <v>423</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>43845</v>
@@ -3060,16 +3060,16 @@
         <v>1</v>
       </c>
       <c r="B6" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="D6" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="10" t="s">
         <v>145</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>146</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>46002</v>
@@ -4804,7 +4804,7 @@
         <v>46313</v>
       </c>
       <c r="J60" s="16" t="s">
-        <v>127</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4815,7 +4815,7 @@
         <v>12</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D61" s="10" t="s">
         <v>54</v>
@@ -4843,7 +4843,7 @@
         <v>12</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>54</v>
@@ -4871,7 +4871,7 @@
         <v>12</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>51</v>
@@ -4899,7 +4899,7 @@
         <v>12</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D64" s="13" t="s">
         <v>54</v>
@@ -4931,7 +4931,7 @@
         <v>12</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>51</v>
@@ -4959,7 +4959,7 @@
         <v>12</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>51</v>
@@ -4987,7 +4987,7 @@
         <v>12</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>54</v>
@@ -5015,7 +5015,7 @@
         <v>12</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>54</v>
@@ -5043,7 +5043,7 @@
         <v>12</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>54</v>
@@ -5071,7 +5071,7 @@
         <v>12</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>51</v>
@@ -5099,7 +5099,7 @@
         <v>12</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D71" s="10" t="s">
         <v>51</v>
@@ -5127,7 +5127,7 @@
         <v>12</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>51</v>
@@ -5155,7 +5155,7 @@
         <v>12</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>117</v>
@@ -5183,7 +5183,7 @@
         <v>12</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>54</v>
@@ -5211,7 +5211,7 @@
         <v>12</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>54</v>
@@ -5239,16 +5239,16 @@
         <v>17</v>
       </c>
       <c r="C76" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="D76" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="D76" s="10" t="s">
+      <c r="E76" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E76" s="10" t="s">
+      <c r="F76" s="10" t="s">
         <v>145</v>
-      </c>
-      <c r="F76" s="10" t="s">
-        <v>146</v>
       </c>
       <c r="G76" s="11" t="n">
         <v>46002</v>
@@ -5267,13 +5267,13 @@
         <v>14</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D77" s="13" t="s">
         <v>34</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F77" s="13" t="s">
         <v>36</v>
@@ -5299,13 +5299,13 @@
         <v>14</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D78" s="16" t="s">
         <v>57</v>
       </c>
       <c r="E78" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F78" s="16" t="s">
         <v>36</v>
@@ -5320,7 +5320,7 @@
         <v>46316</v>
       </c>
       <c r="J78" s="16" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5337,7 +5337,7 @@
         <v>100</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>36</v>
@@ -5365,7 +5365,7 @@
         <v>152</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F80" s="13" t="s">
         <v>153</v>
@@ -5397,7 +5397,7 @@
         <v>95</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>40</v>
@@ -5425,7 +5425,7 @@
         <v>42</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F82" s="10" t="s">
         <v>43</v>
@@ -5453,7 +5453,7 @@
         <v>74</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F83" s="13" t="s">
         <v>43</v>
@@ -5485,7 +5485,7 @@
         <v>158</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F84" s="10" t="s">
         <v>36</v>
@@ -5513,7 +5513,7 @@
         <v>74</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>43</v>
@@ -5541,7 +5541,7 @@
         <v>67</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F86" s="10" t="s">
         <v>63</v>
@@ -5569,7 +5569,7 @@
         <v>34</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F87" s="13" t="s">
         <v>36</v>
@@ -5601,7 +5601,7 @@
         <v>95</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F88" s="10" t="s">
         <v>40</v>
@@ -5629,7 +5629,7 @@
         <v>100</v>
       </c>
       <c r="E89" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F89" s="16" t="s">
         <v>36</v>
@@ -5644,7 +5644,7 @@
         <v>46331</v>
       </c>
       <c r="J89" s="16" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5692,7 +5692,7 @@
         <v>169</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G91" s="11" t="n">
         <v>45098</v>
@@ -5720,7 +5720,7 @@
         <v>169</v>
       </c>
       <c r="F92" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G92" s="11" t="n">
         <v>42849</v>
@@ -5776,7 +5776,7 @@
         <v>169</v>
       </c>
       <c r="F94" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G94" s="11" t="n">
         <v>46086</v>
@@ -5804,7 +5804,7 @@
         <v>169</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G95" s="11" t="n">
         <v>45978</v>
@@ -5832,7 +5832,7 @@
         <v>169</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G96" s="11" t="n">
         <v>45936</v>
@@ -5860,7 +5860,7 @@
         <v>169</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G97" s="11" t="n">
         <v>45930</v>
@@ -10336,7 +10336,7 @@
         <v>423</v>
       </c>
       <c r="F256" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G256" s="11" t="n">
         <v>43283</v>
@@ -10364,7 +10364,7 @@
         <v>423</v>
       </c>
       <c r="F257" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G257" s="11" t="n">
         <v>46065</v>
@@ -10392,7 +10392,7 @@
         <v>423</v>
       </c>
       <c r="F258" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G258" s="11" t="n">
         <v>43845</v>
@@ -10588,7 +10588,7 @@
         <v>441</v>
       </c>
       <c r="F265" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G265" s="11" t="n">
         <v>45446</v>
@@ -10616,7 +10616,7 @@
         <v>441</v>
       </c>
       <c r="F266" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G266" s="11" t="n">
         <v>45944</v>
@@ -10644,7 +10644,7 @@
         <v>441</v>
       </c>
       <c r="F267" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G267" s="11" t="n">
         <v>46104</v>
@@ -10672,7 +10672,7 @@
         <v>441</v>
       </c>
       <c r="F268" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G268" s="11" t="n">
         <v>46113</v>
@@ -11964,7 +11964,7 @@
         <v>46322</v>
       </c>
       <c r="J313" s="16" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12192,7 +12192,7 @@
         <v>46324</v>
       </c>
       <c r="J321" s="16" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12224,7 +12224,7 @@
         <v>46354</v>
       </c>
       <c r="J322" s="16" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12376,7 +12376,7 @@
         <v>46366</v>
       </c>
       <c r="J327" s="16" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12464,7 +12464,7 @@
         <v>46352</v>
       </c>
       <c r="J330" s="16" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12616,7 +12616,7 @@
         <v>46332</v>
       </c>
       <c r="J335" s="16" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -12685,13 +12685,13 @@
         <v>14</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>34</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F5" s="16" t="s">
         <v>536</v>
@@ -12705,13 +12705,13 @@
         <v>14</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F6" s="16" t="s">
         <v>536</v>
@@ -12731,7 +12731,7 @@
         <v>100</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>536</v>
@@ -12751,7 +12751,7 @@
         <v>158</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>537</v>
@@ -12771,7 +12771,7 @@
         <v>34</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F9" s="16" t="s">
         <v>536</v>
@@ -12791,7 +12791,7 @@
         <v>100</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F10" s="16" t="s">
         <v>536</v>
@@ -13947,7 +13947,7 @@
         <v>169</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>45098</v>
@@ -13972,7 +13972,7 @@
         <v>169</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>42849</v>
@@ -14022,7 +14022,7 @@
         <v>169</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>46086</v>
@@ -14047,7 +14047,7 @@
         <v>169</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F10" s="11" t="n">
         <v>45978</v>
@@ -14072,7 +14072,7 @@
         <v>169</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>45936</v>
@@ -14097,7 +14097,7 @@
         <v>169</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F12" s="11" t="n">
         <v>45930</v>
@@ -18600,7 +18600,7 @@
         <v>441</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>45446</v>
@@ -18625,7 +18625,7 @@
         <v>441</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>45944</v>
@@ -18650,7 +18650,7 @@
         <v>441</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>46104</v>
@@ -18675,7 +18675,7 @@
         <v>441</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>46113</v>
@@ -19832,7 +19832,7 @@
         <v>46322</v>
       </c>
       <c r="I54" s="16" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21327,7 +21327,7 @@
         <v>46313</v>
       </c>
       <c r="I51" s="16" t="s">
-        <v>127</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21335,7 +21335,7 @@
         <v>47</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C52" s="10" t="s">
         <v>54</v>
@@ -21360,7 +21360,7 @@
         <v>48</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C53" s="10" t="s">
         <v>54</v>
@@ -21385,7 +21385,7 @@
         <v>49</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C54" s="10" t="s">
         <v>51</v>
@@ -21410,7 +21410,7 @@
         <v>50</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C55" s="13" t="s">
         <v>54</v>
@@ -21439,7 +21439,7 @@
         <v>51</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C56" s="10" t="s">
         <v>51</v>
@@ -21464,7 +21464,7 @@
         <v>52</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C57" s="10" t="s">
         <v>51</v>
@@ -21489,7 +21489,7 @@
         <v>53</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C58" s="10" t="s">
         <v>54</v>
@@ -21514,7 +21514,7 @@
         <v>54</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C59" s="10" t="s">
         <v>54</v>
@@ -21539,7 +21539,7 @@
         <v>55</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C60" s="10" t="s">
         <v>54</v>
@@ -21564,7 +21564,7 @@
         <v>56</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C61" s="10" t="s">
         <v>51</v>
@@ -21589,7 +21589,7 @@
         <v>57</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>51</v>
@@ -21614,7 +21614,7 @@
         <v>58</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C63" s="10" t="s">
         <v>51</v>
@@ -21639,7 +21639,7 @@
         <v>59</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>117</v>
@@ -21664,7 +21664,7 @@
         <v>60</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C65" s="10" t="s">
         <v>54</v>
@@ -21689,7 +21689,7 @@
         <v>61</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>54</v>
@@ -22170,7 +22170,7 @@
         <v>46324</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22199,7 +22199,7 @@
         <v>46354</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22336,7 +22336,7 @@
         <v>46366</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22415,7 +22415,7 @@
         <v>46352</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22552,7 +22552,7 @@
         <v>46332</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22741,13 +22741,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>34</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>36</v>
@@ -22770,13 +22770,13 @@
         <v>2</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>57</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>36</v>
@@ -22791,7 +22791,7 @@
         <v>46316</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22805,7 +22805,7 @@
         <v>100</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>36</v>
@@ -22830,7 +22830,7 @@
         <v>152</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>153</v>
@@ -22859,7 +22859,7 @@
         <v>95</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>40</v>
@@ -22884,7 +22884,7 @@
         <v>42</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>43</v>
@@ -22909,7 +22909,7 @@
         <v>74</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>43</v>
@@ -22938,7 +22938,7 @@
         <v>158</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>36</v>
@@ -22963,7 +22963,7 @@
         <v>74</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>43</v>
@@ -22988,7 +22988,7 @@
         <v>67</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>63</v>
@@ -23013,7 +23013,7 @@
         <v>34</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E16" s="13" t="s">
         <v>36</v>
@@ -23042,7 +23042,7 @@
         <v>95</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>40</v>
@@ -23067,7 +23067,7 @@
         <v>100</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E18" s="16" t="s">
         <v>36</v>
@@ -23082,7 +23082,7 @@
         <v>46331</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23137,13 +23137,13 @@
         <v>1</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C24" s="16" t="s">
         <v>34</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E24" s="16" t="s">
         <v>536</v>
@@ -23154,13 +23154,13 @@
         <v>2</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>57</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E25" s="16" t="s">
         <v>536</v>
@@ -23177,7 +23177,7 @@
         <v>100</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E26" s="16" t="s">
         <v>536</v>
@@ -23194,7 +23194,7 @@
         <v>158</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E27" s="16" t="s">
         <v>537</v>
@@ -23211,7 +23211,7 @@
         <v>34</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>536</v>
@@ -23228,7 +23228,7 @@
         <v>100</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E29" s="16" t="s">
         <v>536</v>

--- a/МО 19.10.2026/Списки МО итог (ред. 19.10.2026).xlsx
+++ b/МО 19.10.2026/Списки МО итог (ред. 19.10.2026).xlsx
@@ -851,10 +851,10 @@
     <t xml:space="preserve">Васильева Алина Владимировна</t>
   </si>
   <si>
+    <t xml:space="preserve">Ермакова Наталья Васильевна</t>
+  </si>
+  <si>
     <t xml:space="preserve">Райкова Ирина Алексеевна</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ермакова Наталья Васильевна</t>
   </si>
   <si>
     <t xml:space="preserve">Шрамко Наталья Викторовна</t>
@@ -7733,7 +7733,7 @@
         <v>63</v>
       </c>
       <c r="G165" s="11" t="n">
-        <v>46097</v>
+        <v>45720</v>
       </c>
       <c r="H165" s="12"/>
       <c r="I165" s="12"/>
@@ -7755,13 +7755,13 @@
         <v>65</v>
       </c>
       <c r="E166" s="10" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="F166" s="10" t="s">
         <v>63</v>
       </c>
       <c r="G166" s="11" t="n">
-        <v>45720</v>
+        <v>46097</v>
       </c>
       <c r="H166" s="12"/>
       <c r="I166" s="12"/>
@@ -7783,7 +7783,7 @@
         <v>65</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>63</v>
@@ -7811,7 +7811,7 @@
         <v>162</v>
       </c>
       <c r="E168" s="10" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="F168" s="10" t="s">
         <v>63</v>
@@ -15715,7 +15715,7 @@
         <v>63</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>46097</v>
+        <v>45720</v>
       </c>
       <c r="G80" s="12"/>
       <c r="H80" s="12"/>
@@ -15734,13 +15734,13 @@
         <v>65</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>63</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>45720</v>
+        <v>46097</v>
       </c>
       <c r="G81" s="12"/>
       <c r="H81" s="12"/>
@@ -15759,7 +15759,7 @@
         <v>65</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="E82" s="10" t="s">
         <v>63</v>
@@ -15784,7 +15784,7 @@
         <v>162</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>63</v>

--- a/МО 19.10.2026/Списки МО итог (ред. 19.10.2026).xlsx
+++ b/МО 19.10.2026/Списки МО итог (ред. 19.10.2026).xlsx
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">п.1 Прил.№2: управление транспортными средствами.</t>
   </si>
   <si>
-    <t xml:space="preserve">п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
+    <t xml:space="preserve">п.1 Прил.№2: управление транспортными средствами.</t>
   </si>
   <si>
     <t xml:space="preserve">Гагарин Алексей Владимирович</t>

--- a/МО 19.10.2026/Списки МО итог (ред. 19.10.2026).xlsx
+++ b/МО 19.10.2026/Списки МО итог (ред. 19.10.2026).xlsx
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">п.1 Прил.№2: управление транспортными средствами.</t>
   </si>
   <si>
-    <t xml:space="preserve">п.1 Прил.№2: управление транспортными средствами.</t>
+    <t xml:space="preserve">п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
   </si>
   <si>
     <t xml:space="preserve">Гагарин Алексей Владимирович</t>

--- a/МО 19.10.2026/Списки МО итог (ред. 19.10.2026).xlsx
+++ b/МО 19.10.2026/Списки МО итог (ред. 19.10.2026).xlsx
@@ -24,7 +24,7 @@
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">'Периодический 2026'!$4:$4</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Периодический 2026'!$A$4:$J$333</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">Психиатрическое!$4:$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Психиатрическое!$A$4:$F$63</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Психиатрическое!$A$4:$F$57</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4336" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4282" uniqueCount="545">
   <si>
     <t xml:space="preserve">Сводка по площадкам: медицинские осмотры и психиатрическое освидетельствование, 2026 год</t>
   </si>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">Склад</t>
   </si>
   <si>
-    <t xml:space="preserve">п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.18.1</t>
+    <t xml:space="preserve">п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2</t>
   </si>
   <si>
     <t xml:space="preserve">Балкивская Людмила Алексеевна</t>
@@ -989,6 +989,9 @@
     <t xml:space="preserve">Каменев Дмитрий Викторович</t>
   </si>
   <si>
+    <t xml:space="preserve">п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.18.1, п.18.2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Карпачева Татьяна Владимировна</t>
   </si>
   <si>
@@ -1010,6 +1013,9 @@
     <t xml:space="preserve">Нестеров Аркадий Николаевич</t>
   </si>
   <si>
+    <t xml:space="preserve">п.4.4, п.5.1, п.6.2, п.18.1, п.18.2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ноженко Екатерина Сергеевна</t>
   </si>
   <si>
@@ -1565,7 +1571,7 @@
     <t xml:space="preserve">Список работников, подлежащих психиатрическому освидетельствованию (графа «Подлежит» = «Да»)</t>
   </si>
   <si>
-    <t xml:space="preserve">Источник: «Учёт медосмотров» на 19.10.2026. Всего: 59 чел.</t>
+    <t xml:space="preserve">Источник: «Учёт медосмотров» на 19.10.2026. Всего: 53 чел.</t>
   </si>
   <si>
     <t xml:space="preserve">Основание (Перечень)</t>
@@ -1580,16 +1586,7 @@
     <t xml:space="preserve">п.1 Прил.№2: управление транспортными средствами.</t>
   </si>
   <si>
-    <t xml:space="preserve">п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Гагарин Алексей Владимирович</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Иванов Дмитрий Сергеевич</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Поляков Александр Валентинович</t>
+    <t xml:space="preserve">п.1 Прил.№2: управление транспортными средствами (погрузчик; п.18.1, п.18.2 приложения к Приказу №29н).</t>
   </si>
   <si>
     <t xml:space="preserve">п.11 Прил.№2: обслуживание электроустановок предприятия.</t>
@@ -1613,7 +1610,7 @@
     <t xml:space="preserve">1. Периодический медицинский осмотр в 2026 году — 165 чел.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Психиатрическое освидетельствование — 24 чел.</t>
+    <t xml:space="preserve">2. Психиатрическое освидетельствование — 21 чел.</t>
   </si>
   <si>
     <t xml:space="preserve">Площадка «Руднево»: медицинские осмотры и психиатрическое освидетельствование, 2026 год</t>
@@ -1622,7 +1619,7 @@
     <t xml:space="preserve">1. Периодический медицинский осмотр в 2026 году — 53 чел.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Психиатрическое освидетельствование — 4 чел.</t>
+    <t xml:space="preserve">2. Психиатрическое освидетельствование — 1 чел.</t>
   </si>
   <si>
     <t xml:space="preserve">Площадка «Воронеж»: медицинские осмотры и психиатрическое освидетельствование, 2026 год</t>
@@ -1665,9 +1662,6 @@
   </si>
   <si>
     <t xml:space="preserve">1. Периодический медицинский осмотр в 2026 году — 9 чел.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Психиатрическое освидетельствование — 1 чел.</t>
   </si>
   <si>
     <t xml:space="preserve">Площадка «Жуковский»: медицинские осмотры и психиатрическое освидетельствование, 2026 год</t>
@@ -1826,95 +1820,95 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2286,8 +2280,8 @@
         <v>22</v>
       </c>
       <c r="H5" s="6" t="n">
-        <f aca="false">COUNTIF(Психиатрическое!$B$5:$B$1000,A5)</f>
-        <v>24</v>
+        <f aca="false">COUNTIF(Психиатрическое!$B$5:$B$994,A5)</f>
+        <v>21</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2318,8 +2312,8 @@
         <v>13</v>
       </c>
       <c r="H6" s="6" t="n">
-        <f aca="false">COUNTIF(Психиатрическое!$B$5:$B$1000,A6)</f>
-        <v>4</v>
+        <f aca="false">COUNTIF(Психиатрическое!$B$5:$B$994,A6)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2350,7 +2344,7 @@
         <v>9</v>
       </c>
       <c r="H7" s="6" t="n">
-        <f aca="false">COUNTIF(Психиатрическое!$B$5:$B$1000,A7)</f>
+        <f aca="false">COUNTIF(Психиатрическое!$B$5:$B$994,A7)</f>
         <v>17</v>
       </c>
     </row>
@@ -2382,7 +2376,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="6" t="n">
-        <f aca="false">COUNTIF(Психиатрическое!$B$5:$B$1000,A8)</f>
+        <f aca="false">COUNTIF(Психиатрическое!$B$5:$B$994,A8)</f>
         <v>5</v>
       </c>
     </row>
@@ -2414,7 +2408,7 @@
         <v>2</v>
       </c>
       <c r="H9" s="6" t="n">
-        <f aca="false">COUNTIF(Психиатрическое!$B$5:$B$1000,A9)</f>
+        <f aca="false">COUNTIF(Психиатрическое!$B$5:$B$994,A9)</f>
         <v>6</v>
       </c>
     </row>
@@ -2446,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="6" t="n">
-        <f aca="false">COUNTIF(Психиатрическое!$B$5:$B$1000,A10)</f>
+        <f aca="false">COUNTIF(Психиатрическое!$B$5:$B$994,A10)</f>
         <v>2</v>
       </c>
     </row>
@@ -2478,7 +2472,7 @@
         <v>2</v>
       </c>
       <c r="H11" s="6" t="n">
-        <f aca="false">COUNTIF(Психиатрическое!$B$5:$B$1000,A11)</f>
+        <f aca="false">COUNTIF(Психиатрическое!$B$5:$B$994,A11)</f>
         <v>1</v>
       </c>
     </row>
@@ -2510,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="6" t="n">
-        <f aca="false">COUNTIF(Психиатрическое!$B$5:$B$1000,A12)</f>
+        <f aca="false">COUNTIF(Психиатрическое!$B$5:$B$994,A12)</f>
         <v>0</v>
       </c>
     </row>
@@ -2544,7 +2538,7 @@
       </c>
       <c r="H13" s="8" t="n">
         <f aca="false">SUM(H5:H12)</f>
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2565,7 +2559,7 @@
         <v>сходится</v>
       </c>
       <c r="H15" s="3" t="str">
-        <f aca="false">IF(H13=COUNTA(Психиатрическое!$C$5:$C$1000),"сходится","ОШИБКА")</f>
+        <f aca="false">IF(H13=COUNTA(Психиатрическое!$C$5:$C$994),"сходится","ОШИБКА")</f>
         <v>сходится</v>
       </c>
     </row>
@@ -2606,17 +2600,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F4" s="22"/>
       <c r="G4" s="22"/>
@@ -2656,13 +2650,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>141</v>
@@ -2681,13 +2675,13 @@
         <v>2</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>413</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>411</v>
-      </c>
       <c r="D7" s="10" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>141</v>
@@ -2706,13 +2700,13 @@
         <v>3</v>
       </c>
       <c r="B8" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>414</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>412</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>141</v>
@@ -2731,13 +2725,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>257</v>
@@ -2756,13 +2750,13 @@
         <v>5</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C10" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>419</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>417</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>257</v>
@@ -2781,13 +2775,13 @@
         <v>6</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>257</v>
@@ -2806,13 +2800,13 @@
         <v>7</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>257</v>
@@ -2831,10 +2825,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>163</v>
@@ -2856,13 +2850,13 @@
         <v>9</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>280</v>
@@ -2878,7 +2872,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="F16" s="22"/>
       <c r="G16" s="22"/>
@@ -2898,7 +2892,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F17" s="22"/>
       <c r="G17" s="22"/>
@@ -2909,16 +2903,16 @@
         <v>1</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F18" s="22"/>
       <c r="G18" s="22"/>
@@ -2957,17 +2951,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="F4" s="22"/>
       <c r="G4" s="22"/>
@@ -3029,7 +3023,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="F8" s="22"/>
       <c r="G8" s="22"/>
@@ -3049,7 +3043,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F9" s="22"/>
       <c r="G9" s="22"/>
@@ -8598,7 +8592,7 @@
         <v>307</v>
       </c>
       <c r="F196" s="10" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="G196" s="11" t="n">
         <v>45805</v>
@@ -8617,7 +8611,7 @@
         <v>10</v>
       </c>
       <c r="C197" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D197" s="10" t="s">
         <v>310</v>
@@ -8645,10 +8639,10 @@
         <v>10</v>
       </c>
       <c r="C198" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D198" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E198" s="10" t="s">
         <v>307</v>
@@ -8673,7 +8667,7 @@
         <v>10</v>
       </c>
       <c r="C199" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D199" s="10" t="s">
         <v>306</v>
@@ -8701,10 +8695,10 @@
         <v>10</v>
       </c>
       <c r="C200" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D200" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E200" s="10" t="s">
         <v>307</v>
@@ -8729,7 +8723,7 @@
         <v>10</v>
       </c>
       <c r="C201" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D201" s="10" t="s">
         <v>306</v>
@@ -8757,7 +8751,7 @@
         <v>10</v>
       </c>
       <c r="C202" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D202" s="10" t="s">
         <v>310</v>
@@ -8766,7 +8760,7 @@
         <v>307</v>
       </c>
       <c r="F202" s="10" t="s">
-        <v>40</v>
+        <v>325</v>
       </c>
       <c r="G202" s="11" t="n">
         <v>44802</v>
@@ -8785,7 +8779,7 @@
         <v>10</v>
       </c>
       <c r="C203" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D203" s="10" t="s">
         <v>77</v>
@@ -8813,10 +8807,10 @@
         <v>10</v>
       </c>
       <c r="C204" s="10" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D204" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E204" s="10" t="s">
         <v>307</v>
@@ -8841,7 +8835,7 @@
         <v>10</v>
       </c>
       <c r="C205" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D205" s="10" t="s">
         <v>77</v>
@@ -8869,7 +8863,7 @@
         <v>10</v>
       </c>
       <c r="C206" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D206" s="10" t="s">
         <v>77</v>
@@ -8897,7 +8891,7 @@
         <v>10</v>
       </c>
       <c r="C207" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D207" s="10" t="s">
         <v>306</v>
@@ -8925,16 +8919,16 @@
         <v>10</v>
       </c>
       <c r="C208" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D208" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E208" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F208" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G208" s="11" t="n">
         <v>41673</v>
@@ -8953,16 +8947,16 @@
         <v>10</v>
       </c>
       <c r="C209" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="D209" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="E209" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="D209" s="10" t="s">
+      <c r="F209" s="10" t="s">
         <v>334</v>
-      </c>
-      <c r="E209" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="F209" s="10" t="s">
-        <v>332</v>
       </c>
       <c r="G209" s="11" t="n">
         <v>45974</v>
@@ -8981,16 +8975,16 @@
         <v>10</v>
       </c>
       <c r="C210" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D210" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E210" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F210" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G210" s="11" t="n">
         <v>45714</v>
@@ -9009,16 +9003,16 @@
         <v>10</v>
       </c>
       <c r="C211" s="10" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D211" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="E211" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="F211" s="10" t="s">
         <v>334</v>
-      </c>
-      <c r="E211" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="F211" s="10" t="s">
-        <v>332</v>
       </c>
       <c r="G211" s="11" t="n">
         <v>45958</v>
@@ -9037,16 +9031,16 @@
         <v>10</v>
       </c>
       <c r="C212" s="10" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D212" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E212" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F212" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G212" s="11" t="n">
         <v>45643</v>
@@ -9065,16 +9059,16 @@
         <v>10</v>
       </c>
       <c r="C213" s="10" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D213" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="E213" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="F213" s="10" t="s">
         <v>334</v>
-      </c>
-      <c r="E213" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="F213" s="10" t="s">
-        <v>332</v>
       </c>
       <c r="G213" s="11" t="n">
         <v>45833</v>
@@ -9093,16 +9087,16 @@
         <v>10</v>
       </c>
       <c r="C214" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D214" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E214" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F214" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G214" s="11" t="n">
         <v>45565</v>
@@ -9121,16 +9115,16 @@
         <v>10</v>
       </c>
       <c r="C215" s="10" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D215" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F215" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G215" s="11" t="n">
         <v>44795</v>
@@ -9149,16 +9143,16 @@
         <v>10</v>
       </c>
       <c r="C216" s="10" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D216" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E216" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F216" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G216" s="11" t="n">
         <v>45587</v>
@@ -9177,16 +9171,16 @@
         <v>10</v>
       </c>
       <c r="C217" s="10" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D217" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F217" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G217" s="11" t="n">
         <v>37438</v>
@@ -9205,16 +9199,16 @@
         <v>10</v>
       </c>
       <c r="C218" s="10" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D218" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="E218" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="F218" s="10" t="s">
         <v>334</v>
-      </c>
-      <c r="E218" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="F218" s="10" t="s">
-        <v>332</v>
       </c>
       <c r="G218" s="11" t="n">
         <v>45714</v>
@@ -9233,16 +9227,16 @@
         <v>10</v>
       </c>
       <c r="C219" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D219" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F219" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G219" s="11" t="n">
         <v>42429</v>
@@ -9261,16 +9255,16 @@
         <v>10</v>
       </c>
       <c r="C220" s="10" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D220" s="10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E220" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F220" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G220" s="11" t="n">
         <v>46036</v>
@@ -9289,16 +9283,16 @@
         <v>10</v>
       </c>
       <c r="C221" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="D221" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="E221" s="10" t="s">
         <v>350</v>
       </c>
-      <c r="D221" s="10" t="s">
+      <c r="F221" s="10" t="s">
         <v>351</v>
-      </c>
-      <c r="E221" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="F221" s="10" t="s">
-        <v>349</v>
       </c>
       <c r="G221" s="11" t="n">
         <v>44621</v>
@@ -9317,16 +9311,16 @@
         <v>10</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D222" s="10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E222" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F222" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G222" s="11" t="n">
         <v>45817</v>
@@ -9345,16 +9339,16 @@
         <v>10</v>
       </c>
       <c r="C223" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D223" s="10" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F223" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G223" s="11" t="n">
         <v>45649</v>
@@ -9373,16 +9367,16 @@
         <v>10</v>
       </c>
       <c r="C224" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="D224" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="D224" s="10" t="s">
-        <v>355</v>
-      </c>
       <c r="E224" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F224" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G224" s="11" t="n">
         <v>46080</v>
@@ -9401,16 +9395,16 @@
         <v>10</v>
       </c>
       <c r="C225" s="10" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D225" s="10" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F225" s="10" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G225" s="11" t="n">
         <v>45748</v>
@@ -9429,16 +9423,16 @@
         <v>10</v>
       </c>
       <c r="C226" s="10" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D226" s="10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E226" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F226" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="G226" s="11" t="n">
         <v>45596</v>
@@ -9457,16 +9451,16 @@
         <v>10</v>
       </c>
       <c r="C227" s="10" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D227" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="E227" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="F227" s="10" t="s">
         <v>351</v>
-      </c>
-      <c r="E227" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="F227" s="10" t="s">
-        <v>349</v>
       </c>
       <c r="G227" s="11" t="n">
         <v>46084</v>
@@ -9485,16 +9479,16 @@
         <v>10</v>
       </c>
       <c r="C228" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D228" s="10" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E228" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F228" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G228" s="11" t="n">
         <v>46064</v>
@@ -9513,16 +9507,16 @@
         <v>10</v>
       </c>
       <c r="C229" s="10" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D229" s="10" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E229" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F229" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G229" s="11" t="n">
         <v>46111</v>
@@ -9541,16 +9535,16 @@
         <v>10</v>
       </c>
       <c r="C230" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="D230" s="10" t="s">
         <v>368</v>
       </c>
-      <c r="D230" s="10" t="s">
-        <v>366</v>
-      </c>
       <c r="E230" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F230" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G230" s="11" t="n">
         <v>46049</v>
@@ -9569,16 +9563,16 @@
         <v>10</v>
       </c>
       <c r="C231" s="10" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D231" s="10" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E231" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F231" s="10" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G231" s="11" t="n">
         <v>46091</v>
@@ -9597,16 +9591,16 @@
         <v>10</v>
       </c>
       <c r="C232" s="10" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D232" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E232" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F232" s="10" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G232" s="11" t="n">
         <v>43040</v>
@@ -9625,16 +9619,16 @@
         <v>10</v>
       </c>
       <c r="C233" s="10" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D233" s="10" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F233" s="10" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="G233" s="11" t="n">
         <v>42388</v>
@@ -9653,13 +9647,13 @@
         <v>10</v>
       </c>
       <c r="C234" s="14" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D234" s="14" t="s">
         <v>34</v>
       </c>
       <c r="E234" s="14" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F234" s="14" t="s">
         <v>36</v>
@@ -9685,13 +9679,13 @@
         <v>10</v>
       </c>
       <c r="C235" s="10" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D235" s="10" t="s">
         <v>34</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F235" s="10" t="s">
         <v>36</v>
@@ -9713,13 +9707,13 @@
         <v>10</v>
       </c>
       <c r="C236" s="10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D236" s="10" t="s">
         <v>34</v>
       </c>
       <c r="E236" s="10" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F236" s="10" t="s">
         <v>36</v>
@@ -9741,13 +9735,13 @@
         <v>10</v>
       </c>
       <c r="C237" s="10" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D237" s="10" t="s">
         <v>34</v>
       </c>
       <c r="E237" s="10" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F237" s="10" t="s">
         <v>36</v>
@@ -9769,13 +9763,13 @@
         <v>10</v>
       </c>
       <c r="C238" s="10" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D238" s="10" t="s">
         <v>186</v>
       </c>
       <c r="E238" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F238" s="10" t="s">
         <v>177</v>
@@ -9797,13 +9791,13 @@
         <v>10</v>
       </c>
       <c r="C239" s="10" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D239" s="10" t="s">
         <v>209</v>
       </c>
       <c r="E239" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F239" s="10" t="s">
         <v>210</v>
@@ -9825,16 +9819,16 @@
         <v>10</v>
       </c>
       <c r="C240" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="D240" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="E240" s="14" t="s">
         <v>385</v>
       </c>
-      <c r="D240" s="14" t="s">
-        <v>386</v>
-      </c>
-      <c r="E240" s="14" t="s">
-        <v>383</v>
-      </c>
       <c r="F240" s="14" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G240" s="15" t="n">
         <v>45952</v>
@@ -9857,13 +9851,13 @@
         <v>10</v>
       </c>
       <c r="C241" s="10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D241" s="10" t="s">
         <v>209</v>
       </c>
       <c r="E241" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F241" s="10" t="s">
         <v>210</v>
@@ -9885,16 +9879,16 @@
         <v>10</v>
       </c>
       <c r="C242" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="D242" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="E242" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="F242" s="10" t="s">
         <v>389</v>
-      </c>
-      <c r="D242" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="E242" s="10" t="s">
-        <v>383</v>
-      </c>
-      <c r="F242" s="10" t="s">
-        <v>387</v>
       </c>
       <c r="G242" s="11" t="n">
         <v>40819</v>
@@ -9913,16 +9907,16 @@
         <v>10</v>
       </c>
       <c r="C243" s="10" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D243" s="10" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E243" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F243" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G243" s="11" t="n">
         <v>45972</v>
@@ -9941,16 +9935,16 @@
         <v>10</v>
       </c>
       <c r="C244" s="10" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D244" s="10" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E244" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F244" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G244" s="11" t="n">
         <v>39420</v>
@@ -9969,16 +9963,16 @@
         <v>10</v>
       </c>
       <c r="C245" s="10" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D245" s="10" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E245" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F245" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G245" s="11" t="n">
         <v>44482</v>
@@ -9997,13 +9991,13 @@
         <v>10</v>
       </c>
       <c r="C246" s="10" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D246" s="10" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E246" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F246" s="10" t="s">
         <v>177</v>
@@ -10025,13 +10019,13 @@
         <v>10</v>
       </c>
       <c r="C247" s="10" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D247" s="10" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E247" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F247" s="10" t="s">
         <v>177</v>
@@ -10053,16 +10047,16 @@
         <v>10</v>
       </c>
       <c r="C248" s="10" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D248" s="10" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E248" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F248" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G248" s="11" t="n">
         <v>45754</v>
@@ -10081,16 +10075,16 @@
         <v>10</v>
       </c>
       <c r="C249" s="10" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D249" s="10" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E249" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F249" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G249" s="11" t="n">
         <v>46136</v>
@@ -10109,16 +10103,16 @@
         <v>10</v>
       </c>
       <c r="C250" s="10" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D250" s="10" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E250" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F250" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G250" s="11" t="n">
         <v>42495</v>
@@ -10137,13 +10131,13 @@
         <v>10</v>
       </c>
       <c r="C251" s="10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D251" s="10" t="s">
         <v>90</v>
       </c>
       <c r="E251" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F251" s="10" t="s">
         <v>63</v>
@@ -10165,16 +10159,16 @@
         <v>10</v>
       </c>
       <c r="C252" s="10" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D252" s="10" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E252" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F252" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G252" s="11" t="n">
         <v>46148</v>
@@ -10193,16 +10187,16 @@
         <v>10</v>
       </c>
       <c r="C253" s="10" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D253" s="10" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E253" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F253" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G253" s="11" t="n">
         <v>45831</v>
@@ -10221,16 +10215,16 @@
         <v>10</v>
       </c>
       <c r="C254" s="10" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D254" s="10" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E254" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F254" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G254" s="11" t="n">
         <v>45428</v>
@@ -10249,16 +10243,16 @@
         <v>10</v>
       </c>
       <c r="C255" s="10" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D255" s="10" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E255" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F255" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G255" s="11" t="n">
         <v>46080</v>
@@ -10277,13 +10271,13 @@
         <v>16</v>
       </c>
       <c r="C256" s="10" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D256" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E256" s="10" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F256" s="10" t="s">
         <v>141</v>
@@ -10305,13 +10299,13 @@
         <v>16</v>
       </c>
       <c r="C257" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="D257" s="10" t="s">
         <v>413</v>
       </c>
-      <c r="D257" s="10" t="s">
-        <v>411</v>
-      </c>
       <c r="E257" s="10" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F257" s="10" t="s">
         <v>141</v>
@@ -10333,13 +10327,13 @@
         <v>16</v>
       </c>
       <c r="C258" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="D258" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="E258" s="10" t="s">
         <v>414</v>
-      </c>
-      <c r="D258" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="E258" s="10" t="s">
-        <v>412</v>
       </c>
       <c r="F258" s="10" t="s">
         <v>141</v>
@@ -10361,13 +10355,13 @@
         <v>16</v>
       </c>
       <c r="C259" s="10" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D259" s="10" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E259" s="10" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F259" s="10" t="s">
         <v>257</v>
@@ -10389,13 +10383,13 @@
         <v>16</v>
       </c>
       <c r="C260" s="10" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D260" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="E260" s="10" t="s">
         <v>419</v>
-      </c>
-      <c r="E260" s="10" t="s">
-        <v>417</v>
       </c>
       <c r="F260" s="10" t="s">
         <v>257</v>
@@ -10417,13 +10411,13 @@
         <v>16</v>
       </c>
       <c r="C261" s="10" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D261" s="10" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E261" s="10" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F261" s="10" t="s">
         <v>257</v>
@@ -10445,13 +10439,13 @@
         <v>16</v>
       </c>
       <c r="C262" s="10" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D262" s="10" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E262" s="10" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F262" s="10" t="s">
         <v>257</v>
@@ -10473,10 +10467,10 @@
         <v>16</v>
       </c>
       <c r="C263" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D263" s="10" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E263" s="10" t="s">
         <v>163</v>
@@ -10501,13 +10495,13 @@
         <v>16</v>
       </c>
       <c r="C264" s="10" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D264" s="10" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E264" s="10" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F264" s="10" t="s">
         <v>280</v>
@@ -10529,10 +10523,10 @@
         <v>11</v>
       </c>
       <c r="C265" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D265" s="10" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E265" s="10" t="s">
         <v>166</v>
@@ -10557,7 +10551,7 @@
         <v>11</v>
       </c>
       <c r="C266" s="10" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D266" s="10" t="s">
         <v>165</v>
@@ -10585,7 +10579,7 @@
         <v>11</v>
       </c>
       <c r="C267" s="10" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D267" s="10" t="s">
         <v>165</v>
@@ -10613,7 +10607,7 @@
         <v>11</v>
       </c>
       <c r="C268" s="10" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D268" s="10" t="s">
         <v>165</v>
@@ -10641,7 +10635,7 @@
         <v>11</v>
       </c>
       <c r="C269" s="10" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D269" s="10" t="s">
         <v>213</v>
@@ -10669,7 +10663,7 @@
         <v>11</v>
       </c>
       <c r="C270" s="10" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D270" s="10" t="s">
         <v>213</v>
@@ -10697,7 +10691,7 @@
         <v>11</v>
       </c>
       <c r="C271" s="10" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D271" s="10" t="s">
         <v>249</v>
@@ -10725,7 +10719,7 @@
         <v>11</v>
       </c>
       <c r="C272" s="14" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D272" s="14" t="s">
         <v>229</v>
@@ -10757,7 +10751,7 @@
         <v>11</v>
       </c>
       <c r="C273" s="10" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D273" s="10" t="s">
         <v>213</v>
@@ -10785,7 +10779,7 @@
         <v>11</v>
       </c>
       <c r="C274" s="10" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D274" s="10" t="s">
         <v>249</v>
@@ -10813,7 +10807,7 @@
         <v>11</v>
       </c>
       <c r="C275" s="14" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D275" s="14" t="s">
         <v>229</v>
@@ -10845,7 +10839,7 @@
         <v>11</v>
       </c>
       <c r="C276" s="10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D276" s="10" t="s">
         <v>249</v>
@@ -10873,7 +10867,7 @@
         <v>11</v>
       </c>
       <c r="C277" s="10" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D277" s="10" t="s">
         <v>194</v>
@@ -10901,7 +10895,7 @@
         <v>11</v>
       </c>
       <c r="C278" s="10" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D278" s="10" t="s">
         <v>194</v>
@@ -10929,7 +10923,7 @@
         <v>11</v>
       </c>
       <c r="C279" s="10" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D279" s="10" t="s">
         <v>213</v>
@@ -10957,7 +10951,7 @@
         <v>11</v>
       </c>
       <c r="C280" s="10" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D280" s="10" t="s">
         <v>229</v>
@@ -10985,7 +10979,7 @@
         <v>11</v>
       </c>
       <c r="C281" s="10" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D281" s="10" t="s">
         <v>213</v>
@@ -11013,7 +11007,7 @@
         <v>11</v>
       </c>
       <c r="C282" s="10" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D282" s="10" t="s">
         <v>162</v>
@@ -11041,7 +11035,7 @@
         <v>11</v>
       </c>
       <c r="C283" s="10" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D283" s="10" t="s">
         <v>293</v>
@@ -11069,10 +11063,10 @@
         <v>11</v>
       </c>
       <c r="C284" s="10" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D284" s="10" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E284" s="10" t="s">
         <v>289</v>
@@ -11097,7 +11091,7 @@
         <v>11</v>
       </c>
       <c r="C285" s="10" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D285" s="10" t="s">
         <v>67</v>
@@ -11125,7 +11119,7 @@
         <v>11</v>
       </c>
       <c r="C286" s="10" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D286" s="10" t="s">
         <v>301</v>
@@ -11153,7 +11147,7 @@
         <v>11</v>
       </c>
       <c r="C287" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D287" s="10" t="s">
         <v>77</v>
@@ -11181,7 +11175,7 @@
         <v>11</v>
       </c>
       <c r="C288" s="10" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D288" s="10" t="s">
         <v>310</v>
@@ -11209,16 +11203,16 @@
         <v>11</v>
       </c>
       <c r="C289" s="10" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D289" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E289" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F289" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G289" s="11" t="n">
         <v>46119</v>
@@ -11237,16 +11231,16 @@
         <v>11</v>
       </c>
       <c r="C290" s="10" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D290" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E290" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F290" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G290" s="11" t="n">
         <v>46055</v>
@@ -11265,16 +11259,16 @@
         <v>11</v>
       </c>
       <c r="C291" s="14" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D291" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E291" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F291" s="14" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G291" s="15" t="n">
         <v>45932</v>
@@ -11297,16 +11291,16 @@
         <v>11</v>
       </c>
       <c r="C292" s="10" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D292" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E292" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F292" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G292" s="11" t="n">
         <v>46094</v>
@@ -11325,16 +11319,16 @@
         <v>11</v>
       </c>
       <c r="C293" s="14" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D293" s="14" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E293" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F293" s="14" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G293" s="15" t="n">
         <v>45931</v>
@@ -11357,13 +11351,13 @@
         <v>11</v>
       </c>
       <c r="C294" s="10" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D294" s="10" t="s">
         <v>51</v>
       </c>
       <c r="E294" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F294" s="10" t="s">
         <v>43</v>
@@ -11385,13 +11379,13 @@
         <v>11</v>
       </c>
       <c r="C295" s="10" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D295" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E295" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F295" s="10" t="s">
         <v>43</v>
@@ -11413,13 +11407,13 @@
         <v>11</v>
       </c>
       <c r="C296" s="10" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D296" s="10" t="s">
         <v>51</v>
       </c>
       <c r="E296" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F296" s="10" t="s">
         <v>43</v>
@@ -11441,13 +11435,13 @@
         <v>11</v>
       </c>
       <c r="C297" s="10" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D297" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E297" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F297" s="10" t="s">
         <v>43</v>
@@ -11469,13 +11463,13 @@
         <v>11</v>
       </c>
       <c r="C298" s="10" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D298" s="10" t="s">
         <v>74</v>
       </c>
       <c r="E298" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F298" s="10" t="s">
         <v>43</v>
@@ -11497,13 +11491,13 @@
         <v>11</v>
       </c>
       <c r="C299" s="14" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D299" s="14" t="s">
         <v>74</v>
       </c>
       <c r="E299" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F299" s="14" t="s">
         <v>43</v>
@@ -11529,13 +11523,13 @@
         <v>11</v>
       </c>
       <c r="C300" s="10" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D300" s="10" t="s">
         <v>51</v>
       </c>
       <c r="E300" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F300" s="10" t="s">
         <v>43</v>
@@ -11557,13 +11551,13 @@
         <v>11</v>
       </c>
       <c r="C301" s="10" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D301" s="10" t="s">
         <v>74</v>
       </c>
       <c r="E301" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F301" s="10" t="s">
         <v>43</v>
@@ -11585,13 +11579,13 @@
         <v>11</v>
       </c>
       <c r="C302" s="10" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D302" s="10" t="s">
         <v>42</v>
       </c>
       <c r="E302" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F302" s="10" t="s">
         <v>43</v>
@@ -11613,13 +11607,13 @@
         <v>11</v>
       </c>
       <c r="C303" s="10" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D303" s="10" t="s">
         <v>51</v>
       </c>
       <c r="E303" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F303" s="10" t="s">
         <v>43</v>
@@ -11641,13 +11635,13 @@
         <v>11</v>
       </c>
       <c r="C304" s="10" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D304" s="10" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E304" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F304" s="10" t="s">
         <v>149</v>
@@ -11669,13 +11663,13 @@
         <v>11</v>
       </c>
       <c r="C305" s="10" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D305" s="10" t="s">
         <v>90</v>
       </c>
       <c r="E305" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F305" s="10" t="s">
         <v>63</v>
@@ -11697,13 +11691,13 @@
         <v>11</v>
       </c>
       <c r="C306" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="D306" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E306" s="10" t="s">
         <v>473</v>
-      </c>
-      <c r="D306" s="10" t="s">
-        <v>470</v>
-      </c>
-      <c r="E306" s="10" t="s">
-        <v>471</v>
       </c>
       <c r="F306" s="10" t="s">
         <v>149</v>
@@ -11725,13 +11719,13 @@
         <v>11</v>
       </c>
       <c r="C307" s="10" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D307" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E307" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F307" s="10" t="s">
         <v>149</v>
@@ -11753,13 +11747,13 @@
         <v>11</v>
       </c>
       <c r="C308" s="10" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D308" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E308" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F308" s="10" t="s">
         <v>149</v>
@@ -11781,13 +11775,13 @@
         <v>11</v>
       </c>
       <c r="C309" s="10" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D309" s="10" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E309" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F309" s="10" t="s">
         <v>149</v>
@@ -11809,13 +11803,13 @@
         <v>11</v>
       </c>
       <c r="C310" s="10" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D310" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E310" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F310" s="10" t="s">
         <v>149</v>
@@ -11837,13 +11831,13 @@
         <v>11</v>
       </c>
       <c r="C311" s="10" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D311" s="10" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E311" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F311" s="10" t="s">
         <v>149</v>
@@ -11865,13 +11859,13 @@
         <v>11</v>
       </c>
       <c r="C312" s="18" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D312" s="18" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E312" s="18" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F312" s="18" t="s">
         <v>149</v>
@@ -11897,13 +11891,13 @@
         <v>11</v>
       </c>
       <c r="C313" s="10" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D313" s="10" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E313" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F313" s="10" t="s">
         <v>149</v>
@@ -11925,13 +11919,13 @@
         <v>11</v>
       </c>
       <c r="C314" s="10" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D314" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E314" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F314" s="10" t="s">
         <v>149</v>
@@ -11953,13 +11947,13 @@
         <v>11</v>
       </c>
       <c r="C315" s="10" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D315" s="10" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E315" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F315" s="10" t="s">
         <v>149</v>
@@ -11981,13 +11975,13 @@
         <v>11</v>
       </c>
       <c r="C316" s="10" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D316" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E316" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F316" s="10" t="s">
         <v>149</v>
@@ -12009,13 +12003,13 @@
         <v>11</v>
       </c>
       <c r="C317" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D317" s="10" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E317" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F317" s="10" t="s">
         <v>149</v>
@@ -12037,7 +12031,7 @@
         <v>13</v>
       </c>
       <c r="C318" s="10" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D318" s="10" t="s">
         <v>61</v>
@@ -12065,13 +12059,13 @@
         <v>13</v>
       </c>
       <c r="C319" s="10" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D319" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E319" s="10" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F319" s="10" t="s">
         <v>63</v>
@@ -12093,13 +12087,13 @@
         <v>13</v>
       </c>
       <c r="C320" s="18" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D320" s="18" t="s">
         <v>74</v>
       </c>
       <c r="E320" s="18" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F320" s="18" t="s">
         <v>43</v>
@@ -12125,13 +12119,13 @@
         <v>13</v>
       </c>
       <c r="C321" s="18" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D321" s="18" t="s">
         <v>74</v>
       </c>
       <c r="E321" s="18" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F321" s="18" t="s">
         <v>43</v>
@@ -12157,13 +12151,13 @@
         <v>13</v>
       </c>
       <c r="C322" s="14" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D322" s="14" t="s">
         <v>74</v>
       </c>
       <c r="E322" s="14" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F322" s="14" t="s">
         <v>43</v>
@@ -12189,13 +12183,13 @@
         <v>13</v>
       </c>
       <c r="C323" s="10" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D323" s="10" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E323" s="10" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F323" s="10" t="s">
         <v>43</v>
@@ -12217,13 +12211,13 @@
         <v>13</v>
       </c>
       <c r="C324" s="14" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D324" s="14" t="s">
         <v>74</v>
       </c>
       <c r="E324" s="14" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F324" s="14" t="s">
         <v>43</v>
@@ -12249,13 +12243,13 @@
         <v>13</v>
       </c>
       <c r="C325" s="10" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D325" s="10" t="s">
         <v>74</v>
       </c>
       <c r="E325" s="10" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F325" s="10" t="s">
         <v>43</v>
@@ -12277,13 +12271,13 @@
         <v>13</v>
       </c>
       <c r="C326" s="18" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D326" s="18" t="s">
         <v>74</v>
       </c>
       <c r="E326" s="18" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F326" s="18" t="s">
         <v>43</v>
@@ -12309,13 +12303,13 @@
         <v>13</v>
       </c>
       <c r="C327" s="10" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D327" s="10" t="s">
         <v>74</v>
       </c>
       <c r="E327" s="10" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F327" s="10" t="s">
         <v>43</v>
@@ -12337,13 +12331,13 @@
         <v>13</v>
       </c>
       <c r="C328" s="18" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D328" s="18" t="s">
         <v>77</v>
       </c>
       <c r="E328" s="18" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F328" s="18" t="s">
         <v>40</v>
@@ -12369,13 +12363,13 @@
         <v>13</v>
       </c>
       <c r="C329" s="10" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D329" s="10" t="s">
         <v>82</v>
       </c>
       <c r="E329" s="10" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F329" s="10" t="s">
         <v>36</v>
@@ -12397,13 +12391,13 @@
         <v>13</v>
       </c>
       <c r="C330" s="14" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D330" s="14" t="s">
         <v>82</v>
       </c>
       <c r="E330" s="14" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F330" s="14" t="s">
         <v>36</v>
@@ -12429,13 +12423,13 @@
         <v>13</v>
       </c>
       <c r="C331" s="14" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D331" s="14" t="s">
         <v>82</v>
       </c>
       <c r="E331" s="14" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F331" s="14" t="s">
         <v>36</v>
@@ -12461,13 +12455,13 @@
         <v>13</v>
       </c>
       <c r="C332" s="10" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D332" s="10" t="s">
         <v>34</v>
       </c>
       <c r="E332" s="10" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F332" s="10" t="s">
         <v>36</v>
@@ -12489,13 +12483,13 @@
         <v>13</v>
       </c>
       <c r="C333" s="18" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D333" s="18" t="s">
         <v>82</v>
       </c>
       <c r="E333" s="18" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F333" s="18" t="s">
         <v>36</v>
@@ -12533,7 +12527,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -12545,12 +12539,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12570,7 +12564,7 @@
         <v>27</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12590,7 +12584,7 @@
         <v>143</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12610,7 +12604,7 @@
         <v>143</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12630,7 +12624,7 @@
         <v>143</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12650,7 +12644,7 @@
         <v>143</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12670,7 +12664,7 @@
         <v>143</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12690,7 +12684,7 @@
         <v>143</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12710,7 +12704,7 @@
         <v>277</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12730,7 +12724,7 @@
         <v>277</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12750,7 +12744,7 @@
         <v>277</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12770,7 +12764,7 @@
         <v>277</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12790,7 +12784,7 @@
         <v>277</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12810,7 +12804,7 @@
         <v>277</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12830,7 +12824,7 @@
         <v>277</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12850,7 +12844,7 @@
         <v>277</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12870,7 +12864,7 @@
         <v>277</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12881,16 +12875,16 @@
         <v>16</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12910,7 +12904,7 @@
         <v>35</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12930,7 +12924,7 @@
         <v>35</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12941,7 +12935,7 @@
         <v>10</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="D23" s="18" t="s">
         <v>306</v>
@@ -12950,7 +12944,7 @@
         <v>307</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12958,19 +12952,19 @@
         <v>20</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>515</v>
+        <v>324</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E24" s="18" t="s">
         <v>307</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12978,19 +12972,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>516</v>
+        <v>348</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>306</v>
+        <v>349</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>307</v>
+        <v>350</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13001,16 +12995,16 @@
         <v>10</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>316</v>
+        <v>352</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>306</v>
+        <v>353</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>307</v>
+        <v>350</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13021,16 +13015,16 @@
         <v>10</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>320</v>
+        <v>354</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>306</v>
+        <v>355</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>307</v>
+        <v>350</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13041,16 +13035,16 @@
         <v>10</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>322</v>
+        <v>360</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>306</v>
+        <v>361</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>307</v>
+        <v>350</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13058,19 +13052,19 @@
         <v>25</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C29" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>350</v>
+      </c>
+      <c r="F29" s="18" t="s">
         <v>517</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>306</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13078,19 +13072,19 @@
         <v>26</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>328</v>
+        <v>519</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>306</v>
+        <v>353</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>307</v>
+        <v>350</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13101,16 +13095,16 @@
         <v>10</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>347</v>
+        <v>34</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13121,16 +13115,16 @@
         <v>10</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>350</v>
+        <v>520</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>351</v>
+        <v>90</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
       <c r="F32" s="18" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13141,16 +13135,16 @@
         <v>10</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>352</v>
+        <v>381</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>353</v>
+        <v>34</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13161,16 +13155,16 @@
         <v>10</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>359</v>
+        <v>34</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
       <c r="F34" s="18" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13181,16 +13175,16 @@
         <v>10</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>351</v>
+        <v>34</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13198,19 +13192,19 @@
         <v>32</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>520</v>
+        <v>79</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>351</v>
+        <v>34</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>348</v>
+        <v>80</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13218,19 +13212,19 @@
         <v>33</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>377</v>
+        <v>81</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>378</v>
+        <v>80</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13238,19 +13232,19 @@
         <v>34</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>521</v>
+        <v>83</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>378</v>
+        <v>80</v>
       </c>
       <c r="F38" s="18" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13258,19 +13252,19 @@
         <v>35</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>379</v>
+        <v>84</v>
       </c>
       <c r="D39" s="18" t="s">
         <v>34</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>378</v>
+        <v>80</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13278,19 +13272,19 @@
         <v>36</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>380</v>
+        <v>85</v>
       </c>
       <c r="D40" s="18" t="s">
         <v>34</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>378</v>
+        <v>80</v>
       </c>
       <c r="F40" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13298,19 +13292,19 @@
         <v>37</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>381</v>
+        <v>86</v>
       </c>
       <c r="D41" s="18" t="s">
         <v>34</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>378</v>
+        <v>80</v>
       </c>
       <c r="F41" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13321,16 +13315,16 @@
         <v>12</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D42" s="18" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E42" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F42" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13341,16 +13335,16 @@
         <v>12</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="E43" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F43" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13361,16 +13355,16 @@
         <v>12</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F44" s="18" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13381,16 +13375,16 @@
         <v>12</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E45" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F45" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13401,7 +13395,7 @@
         <v>12</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D46" s="18" t="s">
         <v>34</v>
@@ -13410,7 +13404,7 @@
         <v>80</v>
       </c>
       <c r="F46" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13421,7 +13415,7 @@
         <v>12</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D47" s="18" t="s">
         <v>34</v>
@@ -13430,7 +13424,7 @@
         <v>80</v>
       </c>
       <c r="F47" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13441,16 +13435,16 @@
         <v>12</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E48" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F48" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13461,7 +13455,7 @@
         <v>12</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D49" s="18" t="s">
         <v>57</v>
@@ -13470,7 +13464,7 @@
         <v>80</v>
       </c>
       <c r="F49" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13481,16 +13475,16 @@
         <v>12</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="E50" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F50" s="18" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13501,7 +13495,7 @@
         <v>12</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D51" s="18" t="s">
         <v>57</v>
@@ -13510,7 +13504,7 @@
         <v>80</v>
       </c>
       <c r="F51" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13521,16 +13515,16 @@
         <v>12</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E52" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F52" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13538,19 +13532,19 @@
         <v>49</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>93</v>
+        <v>504</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>80</v>
+        <v>505</v>
       </c>
       <c r="F53" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13558,19 +13552,19 @@
         <v>50</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>94</v>
+        <v>506</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="E54" s="18" t="s">
-        <v>80</v>
+        <v>505</v>
       </c>
       <c r="F54" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13578,19 +13572,19 @@
         <v>51</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>95</v>
+        <v>507</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>80</v>
+        <v>505</v>
       </c>
       <c r="F55" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13598,19 +13592,19 @@
         <v>52</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>96</v>
+        <v>508</v>
       </c>
       <c r="D56" s="18" t="s">
         <v>34</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>80</v>
+        <v>505</v>
       </c>
       <c r="F56" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13618,143 +13612,29 @@
         <v>53</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>97</v>
+        <v>509</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>80</v>
+        <v>505</v>
       </c>
       <c r="F57" s="18" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="17" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C58" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="D58" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="E58" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="F58" s="18" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="17" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C59" s="18" t="s">
-        <v>502</v>
-      </c>
-      <c r="D59" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="E59" s="18" t="s">
-        <v>503</v>
-      </c>
-      <c r="F59" s="18" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="17" t="n">
-        <v>56</v>
-      </c>
-      <c r="B60" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C60" s="18" t="s">
-        <v>504</v>
-      </c>
-      <c r="D60" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="E60" s="18" t="s">
-        <v>503</v>
-      </c>
-      <c r="F60" s="18" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="17" t="n">
-        <v>57</v>
-      </c>
-      <c r="B61" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="18" t="s">
-        <v>505</v>
-      </c>
-      <c r="D61" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="E61" s="18" t="s">
-        <v>503</v>
-      </c>
-      <c r="F61" s="18" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="17" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="18" t="s">
-        <v>506</v>
-      </c>
-      <c r="D62" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="E62" s="18" t="s">
-        <v>503</v>
-      </c>
-      <c r="F62" s="18" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="17" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="18" t="s">
-        <v>507</v>
-      </c>
-      <c r="D63" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="E63" s="18" t="s">
-        <v>503</v>
-      </c>
-      <c r="F63" s="18" t="s">
-        <v>511</v>
-      </c>
-    </row>
+        <v>513</v>
+      </c>
+    </row>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A4:F63"/>
+  <autoFilter ref="A4:F57"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -13771,7 +13651,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:I198"/>
+  <dimension ref="A1:I1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -13787,17 +13667,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F4" s="22"/>
       <c r="G4" s="22"/>
@@ -16487,7 +16367,7 @@
         <v>307</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="F111" s="11" t="n">
         <v>45805</v>
@@ -16503,7 +16383,7 @@
         <v>107</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C112" s="10" t="s">
         <v>310</v>
@@ -16528,10 +16408,10 @@
         <v>108</v>
       </c>
       <c r="B113" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D113" s="10" t="s">
         <v>307</v>
@@ -16553,7 +16433,7 @@
         <v>109</v>
       </c>
       <c r="B114" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C114" s="10" t="s">
         <v>306</v>
@@ -16578,10 +16458,10 @@
         <v>110</v>
       </c>
       <c r="B115" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D115" s="10" t="s">
         <v>307</v>
@@ -16603,7 +16483,7 @@
         <v>111</v>
       </c>
       <c r="B116" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C116" s="10" t="s">
         <v>306</v>
@@ -16628,7 +16508,7 @@
         <v>112</v>
       </c>
       <c r="B117" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C117" s="10" t="s">
         <v>310</v>
@@ -16637,7 +16517,7 @@
         <v>307</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>40</v>
+        <v>325</v>
       </c>
       <c r="F117" s="11" t="n">
         <v>44802</v>
@@ -16653,7 +16533,7 @@
         <v>113</v>
       </c>
       <c r="B118" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C118" s="10" t="s">
         <v>77</v>
@@ -16678,10 +16558,10 @@
         <v>114</v>
       </c>
       <c r="B119" s="10" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D119" s="10" t="s">
         <v>307</v>
@@ -16703,7 +16583,7 @@
         <v>115</v>
       </c>
       <c r="B120" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C120" s="10" t="s">
         <v>77</v>
@@ -16728,7 +16608,7 @@
         <v>116</v>
       </c>
       <c r="B121" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C121" s="10" t="s">
         <v>77</v>
@@ -16753,7 +16633,7 @@
         <v>117</v>
       </c>
       <c r="B122" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C122" s="10" t="s">
         <v>306</v>
@@ -16778,16 +16658,16 @@
         <v>118</v>
       </c>
       <c r="B123" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F123" s="11" t="n">
         <v>41673</v>
@@ -16803,16 +16683,16 @@
         <v>119</v>
       </c>
       <c r="B124" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="C124" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="D124" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="C124" s="10" t="s">
+      <c r="E124" s="10" t="s">
         <v>334</v>
-      </c>
-      <c r="D124" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="E124" s="10" t="s">
-        <v>332</v>
       </c>
       <c r="F124" s="11" t="n">
         <v>45974</v>
@@ -16828,16 +16708,16 @@
         <v>120</v>
       </c>
       <c r="B125" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F125" s="11" t="n">
         <v>45714</v>
@@ -16853,16 +16733,16 @@
         <v>121</v>
       </c>
       <c r="B126" s="10" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C126" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="D126" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="E126" s="10" t="s">
         <v>334</v>
-      </c>
-      <c r="D126" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="E126" s="10" t="s">
-        <v>332</v>
       </c>
       <c r="F126" s="11" t="n">
         <v>45958</v>
@@ -16878,16 +16758,16 @@
         <v>122</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F127" s="11" t="n">
         <v>45643</v>
@@ -16903,16 +16783,16 @@
         <v>123</v>
       </c>
       <c r="B128" s="10" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C128" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="D128" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="E128" s="10" t="s">
         <v>334</v>
-      </c>
-      <c r="D128" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="E128" s="10" t="s">
-        <v>332</v>
       </c>
       <c r="F128" s="11" t="n">
         <v>45833</v>
@@ -16928,16 +16808,16 @@
         <v>124</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F129" s="11" t="n">
         <v>45565</v>
@@ -16953,16 +16833,16 @@
         <v>125</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E130" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F130" s="11" t="n">
         <v>44795</v>
@@ -16978,16 +16858,16 @@
         <v>126</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F131" s="11" t="n">
         <v>45587</v>
@@ -17003,16 +16883,16 @@
         <v>127</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D132" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F132" s="11" t="n">
         <v>37438</v>
@@ -17028,16 +16908,16 @@
         <v>128</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C133" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="D133" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="E133" s="10" t="s">
         <v>334</v>
-      </c>
-      <c r="D133" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="E133" s="10" t="s">
-        <v>332</v>
       </c>
       <c r="F133" s="11" t="n">
         <v>45714</v>
@@ -17053,16 +16933,16 @@
         <v>129</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D134" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E134" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F134" s="11" t="n">
         <v>42429</v>
@@ -17078,16 +16958,16 @@
         <v>130</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F135" s="11" t="n">
         <v>46036</v>
@@ -17103,16 +16983,16 @@
         <v>131</v>
       </c>
       <c r="B136" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="C136" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="D136" s="10" t="s">
         <v>350</v>
       </c>
-      <c r="C136" s="10" t="s">
+      <c r="E136" s="10" t="s">
         <v>351</v>
-      </c>
-      <c r="D136" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="E136" s="10" t="s">
-        <v>349</v>
       </c>
       <c r="F136" s="11" t="n">
         <v>44621</v>
@@ -17128,16 +17008,16 @@
         <v>132</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D137" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F137" s="11" t="n">
         <v>45817</v>
@@ -17153,16 +17033,16 @@
         <v>133</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D138" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E138" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F138" s="11" t="n">
         <v>45649</v>
@@ -17178,16 +17058,16 @@
         <v>134</v>
       </c>
       <c r="B139" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="C139" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="C139" s="10" t="s">
-        <v>355</v>
-      </c>
       <c r="D139" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F139" s="11" t="n">
         <v>46080</v>
@@ -17203,16 +17083,16 @@
         <v>135</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E140" s="10" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F140" s="11" t="n">
         <v>45748</v>
@@ -17228,16 +17108,16 @@
         <v>136</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D141" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F141" s="11" t="n">
         <v>45596</v>
@@ -17253,16 +17133,16 @@
         <v>137</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C142" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="D142" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="E142" s="10" t="s">
         <v>351</v>
-      </c>
-      <c r="D142" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="E142" s="10" t="s">
-        <v>349</v>
       </c>
       <c r="F142" s="11" t="n">
         <v>46084</v>
@@ -17278,16 +17158,16 @@
         <v>138</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D143" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F143" s="11" t="n">
         <v>46064</v>
@@ -17303,16 +17183,16 @@
         <v>139</v>
       </c>
       <c r="B144" s="10" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D144" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E144" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F144" s="11" t="n">
         <v>46111</v>
@@ -17328,16 +17208,16 @@
         <v>140</v>
       </c>
       <c r="B145" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="C145" s="10" t="s">
         <v>368</v>
       </c>
-      <c r="C145" s="10" t="s">
-        <v>366</v>
-      </c>
       <c r="D145" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F145" s="11" t="n">
         <v>46049</v>
@@ -17353,16 +17233,16 @@
         <v>141</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C146" s="10" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D146" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E146" s="10" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F146" s="11" t="n">
         <v>46091</v>
@@ -17378,16 +17258,16 @@
         <v>142</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D147" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F147" s="11" t="n">
         <v>43040</v>
@@ -17403,16 +17283,16 @@
         <v>143</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D148" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E148" s="10" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F148" s="11" t="n">
         <v>42388</v>
@@ -17428,13 +17308,13 @@
         <v>144</v>
       </c>
       <c r="B149" s="14" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C149" s="14" t="s">
         <v>34</v>
       </c>
       <c r="D149" s="14" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E149" s="14" t="s">
         <v>36</v>
@@ -17457,13 +17337,13 @@
         <v>145</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C150" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D150" s="10" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E150" s="10" t="s">
         <v>36</v>
@@ -17482,13 +17362,13 @@
         <v>146</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C151" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D151" s="10" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>36</v>
@@ -17507,13 +17387,13 @@
         <v>147</v>
       </c>
       <c r="B152" s="10" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C152" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D152" s="10" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E152" s="10" t="s">
         <v>36</v>
@@ -17532,13 +17412,13 @@
         <v>148</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C153" s="10" t="s">
         <v>186</v>
       </c>
       <c r="D153" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>177</v>
@@ -17557,13 +17437,13 @@
         <v>149</v>
       </c>
       <c r="B154" s="10" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C154" s="10" t="s">
         <v>209</v>
       </c>
       <c r="D154" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E154" s="10" t="s">
         <v>210</v>
@@ -17582,16 +17462,16 @@
         <v>150</v>
       </c>
       <c r="B155" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="C155" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="D155" s="14" t="s">
         <v>385</v>
       </c>
-      <c r="C155" s="14" t="s">
-        <v>386</v>
-      </c>
-      <c r="D155" s="14" t="s">
-        <v>383</v>
-      </c>
       <c r="E155" s="14" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F155" s="15" t="n">
         <v>45952</v>
@@ -17611,13 +17491,13 @@
         <v>151</v>
       </c>
       <c r="B156" s="10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C156" s="10" t="s">
         <v>209</v>
       </c>
       <c r="D156" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E156" s="10" t="s">
         <v>210</v>
@@ -17636,16 +17516,16 @@
         <v>152</v>
       </c>
       <c r="B157" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="C157" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="D157" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="E157" s="10" t="s">
         <v>389</v>
-      </c>
-      <c r="C157" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="D157" s="10" t="s">
-        <v>383</v>
-      </c>
-      <c r="E157" s="10" t="s">
-        <v>387</v>
       </c>
       <c r="F157" s="11" t="n">
         <v>40819</v>
@@ -17661,16 +17541,16 @@
         <v>153</v>
       </c>
       <c r="B158" s="10" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D158" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E158" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F158" s="11" t="n">
         <v>45972</v>
@@ -17686,16 +17566,16 @@
         <v>154</v>
       </c>
       <c r="B159" s="10" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D159" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F159" s="11" t="n">
         <v>39420</v>
@@ -17711,16 +17591,16 @@
         <v>155</v>
       </c>
       <c r="B160" s="10" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C160" s="10" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D160" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E160" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F160" s="11" t="n">
         <v>44482</v>
@@ -17736,13 +17616,13 @@
         <v>156</v>
       </c>
       <c r="B161" s="10" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C161" s="10" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D161" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E161" s="10" t="s">
         <v>177</v>
@@ -17761,13 +17641,13 @@
         <v>157</v>
       </c>
       <c r="B162" s="10" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C162" s="10" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D162" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E162" s="10" t="s">
         <v>177</v>
@@ -17786,16 +17666,16 @@
         <v>158</v>
       </c>
       <c r="B163" s="10" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C163" s="10" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D163" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F163" s="11" t="n">
         <v>45754</v>
@@ -17811,16 +17691,16 @@
         <v>159</v>
       </c>
       <c r="B164" s="10" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C164" s="10" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D164" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E164" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F164" s="11" t="n">
         <v>46136</v>
@@ -17836,16 +17716,16 @@
         <v>160</v>
       </c>
       <c r="B165" s="10" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C165" s="10" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D165" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F165" s="11" t="n">
         <v>42495</v>
@@ -17861,13 +17741,13 @@
         <v>161</v>
       </c>
       <c r="B166" s="10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C166" s="10" t="s">
         <v>90</v>
       </c>
       <c r="D166" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E166" s="10" t="s">
         <v>63</v>
@@ -17886,16 +17766,16 @@
         <v>162</v>
       </c>
       <c r="B167" s="10" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C167" s="10" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D167" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F167" s="11" t="n">
         <v>46148</v>
@@ -17911,16 +17791,16 @@
         <v>163</v>
       </c>
       <c r="B168" s="10" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C168" s="10" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D168" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E168" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F168" s="11" t="n">
         <v>45831</v>
@@ -17936,16 +17816,16 @@
         <v>164</v>
       </c>
       <c r="B169" s="10" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C169" s="10" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D169" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F169" s="11" t="n">
         <v>45428</v>
@@ -17961,16 +17841,16 @@
         <v>165</v>
       </c>
       <c r="B170" s="10" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C170" s="10" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D170" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E170" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F170" s="11" t="n">
         <v>46080</v>
@@ -17983,7 +17863,7 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="21" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F172" s="22"/>
       <c r="G172" s="22"/>
@@ -18003,7 +17883,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F173" s="22"/>
       <c r="G173" s="22"/>
@@ -18023,7 +17903,7 @@
         <v>277</v>
       </c>
       <c r="E174" s="18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F174" s="22"/>
       <c r="G174" s="22"/>
@@ -18043,7 +17923,7 @@
         <v>277</v>
       </c>
       <c r="E175" s="18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F175" s="22"/>
       <c r="G175" s="22"/>
@@ -18063,7 +17943,7 @@
         <v>277</v>
       </c>
       <c r="E176" s="18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F176" s="22"/>
       <c r="G176" s="22"/>
@@ -18083,7 +17963,7 @@
         <v>277</v>
       </c>
       <c r="E177" s="18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F177" s="22"/>
       <c r="G177" s="22"/>
@@ -18103,7 +17983,7 @@
         <v>277</v>
       </c>
       <c r="E178" s="18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F178" s="22"/>
       <c r="G178" s="22"/>
@@ -18123,7 +18003,7 @@
         <v>277</v>
       </c>
       <c r="E179" s="18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F179" s="22"/>
       <c r="G179" s="22"/>
@@ -18143,7 +18023,7 @@
         <v>277</v>
       </c>
       <c r="E180" s="18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F180" s="22"/>
       <c r="G180" s="22"/>
@@ -18163,7 +18043,7 @@
         <v>277</v>
       </c>
       <c r="E181" s="18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F181" s="22"/>
       <c r="G181" s="22"/>
@@ -18183,7 +18063,7 @@
         <v>277</v>
       </c>
       <c r="E182" s="18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F182" s="22"/>
       <c r="G182" s="22"/>
@@ -18194,7 +18074,7 @@
         <v>10</v>
       </c>
       <c r="B183" s="18" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="C183" s="18" t="s">
         <v>306</v>
@@ -18203,7 +18083,7 @@
         <v>307</v>
       </c>
       <c r="E183" s="18" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F183" s="22"/>
       <c r="G183" s="22"/>
@@ -18214,16 +18094,16 @@
         <v>11</v>
       </c>
       <c r="B184" s="18" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C184" s="18" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D184" s="18" t="s">
         <v>307</v>
       </c>
       <c r="E184" s="18" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F184" s="22"/>
       <c r="G184" s="22"/>
@@ -18234,16 +18114,16 @@
         <v>12</v>
       </c>
       <c r="B185" s="18" t="s">
-        <v>320</v>
+        <v>348</v>
       </c>
       <c r="C185" s="18" t="s">
-        <v>306</v>
+        <v>349</v>
       </c>
       <c r="D185" s="18" t="s">
-        <v>307</v>
+        <v>350</v>
       </c>
       <c r="E185" s="18" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F185" s="22"/>
       <c r="G185" s="22"/>
@@ -18254,16 +18134,16 @@
         <v>13</v>
       </c>
       <c r="B186" s="18" t="s">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="C186" s="18" t="s">
-        <v>306</v>
+        <v>353</v>
       </c>
       <c r="D186" s="18" t="s">
-        <v>307</v>
+        <v>350</v>
       </c>
       <c r="E186" s="18" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F186" s="22"/>
       <c r="G186" s="22"/>
@@ -18274,16 +18154,16 @@
         <v>14</v>
       </c>
       <c r="B187" s="18" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="C187" s="18" t="s">
-        <v>306</v>
+        <v>355</v>
       </c>
       <c r="D187" s="18" t="s">
-        <v>307</v>
+        <v>350</v>
       </c>
       <c r="E187" s="18" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F187" s="22"/>
       <c r="G187" s="22"/>
@@ -18294,13 +18174,13 @@
         <v>15</v>
       </c>
       <c r="B188" s="18" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="C188" s="18" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="D188" s="18" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E188" s="18" t="s">
         <v>518</v>
@@ -18314,16 +18194,16 @@
         <v>16</v>
       </c>
       <c r="B189" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="C189" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="D189" s="18" t="s">
         <v>350</v>
       </c>
-      <c r="C189" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="D189" s="18" t="s">
-        <v>348</v>
-      </c>
       <c r="E189" s="18" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F189" s="22"/>
       <c r="G189" s="22"/>
@@ -18334,16 +18214,16 @@
         <v>17</v>
       </c>
       <c r="B190" s="18" t="s">
-        <v>352</v>
+        <v>379</v>
       </c>
       <c r="C190" s="18" t="s">
-        <v>353</v>
+        <v>34</v>
       </c>
       <c r="D190" s="18" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
       <c r="E190" s="18" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="F190" s="22"/>
       <c r="G190" s="22"/>
@@ -18354,16 +18234,16 @@
         <v>18</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>358</v>
+        <v>520</v>
       </c>
       <c r="C191" s="18" t="s">
-        <v>359</v>
+        <v>90</v>
       </c>
       <c r="D191" s="18" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
       <c r="E191" s="18" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="F191" s="22"/>
       <c r="G191" s="22"/>
@@ -18374,16 +18254,16 @@
         <v>19</v>
       </c>
       <c r="B192" s="18" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="C192" s="18" t="s">
-        <v>351</v>
+        <v>34</v>
       </c>
       <c r="D192" s="18" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
       <c r="E192" s="18" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="F192" s="22"/>
       <c r="G192" s="22"/>
@@ -18394,16 +18274,16 @@
         <v>20</v>
       </c>
       <c r="B193" s="18" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C193" s="18" t="s">
         <v>34</v>
       </c>
       <c r="D193" s="18" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E193" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F193" s="22"/>
       <c r="G193" s="22"/>
@@ -18414,82 +18294,25 @@
         <v>21</v>
       </c>
       <c r="B194" s="18" t="s">
-        <v>521</v>
+        <v>383</v>
       </c>
       <c r="C194" s="18" t="s">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="D194" s="18" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E194" s="18" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F194" s="22"/>
       <c r="G194" s="22"/>
       <c r="H194" s="22"/>
     </row>
-    <row r="195" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A195" s="17" t="n">
-        <v>22</v>
-      </c>
-      <c r="B195" s="18" t="s">
-        <v>379</v>
-      </c>
-      <c r="C195" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D195" s="18" t="s">
-        <v>378</v>
-      </c>
-      <c r="E195" s="18" t="s">
-        <v>511</v>
-      </c>
-      <c r="F195" s="22"/>
-      <c r="G195" s="22"/>
-      <c r="H195" s="22"/>
-    </row>
-    <row r="196" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A196" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="B196" s="18" t="s">
-        <v>380</v>
-      </c>
-      <c r="C196" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D196" s="18" t="s">
-        <v>378</v>
-      </c>
-      <c r="E196" s="18" t="s">
-        <v>511</v>
-      </c>
-      <c r="F196" s="22"/>
-      <c r="G196" s="22"/>
-      <c r="H196" s="22"/>
-    </row>
-    <row r="197" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A197" s="17" t="n">
-        <v>24</v>
-      </c>
-      <c r="B197" s="18" t="s">
-        <v>381</v>
-      </c>
-      <c r="C197" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D197" s="18" t="s">
-        <v>378</v>
-      </c>
-      <c r="E197" s="18" t="s">
-        <v>511</v>
-      </c>
-      <c r="F197" s="22"/>
-      <c r="G197" s="22"/>
-      <c r="H197" s="22"/>
-    </row>
-    <row r="198" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="195" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -18506,7 +18329,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -18522,17 +18345,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F4" s="22"/>
       <c r="G4" s="22"/>
@@ -18572,10 +18395,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>166</v>
@@ -18597,7 +18420,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>165</v>
@@ -18622,7 +18445,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>165</v>
@@ -18647,7 +18470,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>165</v>
@@ -18672,7 +18495,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>213</v>
@@ -18697,7 +18520,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>213</v>
@@ -18722,7 +18545,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>249</v>
@@ -18747,7 +18570,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>229</v>
@@ -18776,7 +18599,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>213</v>
@@ -18801,7 +18624,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>249</v>
@@ -18826,7 +18649,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>229</v>
@@ -18855,7 +18678,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>249</v>
@@ -18880,7 +18703,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>194</v>
@@ -18905,7 +18728,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>194</v>
@@ -18930,7 +18753,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>213</v>
@@ -18955,7 +18778,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>229</v>
@@ -18980,7 +18803,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>213</v>
@@ -19005,7 +18828,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>162</v>
@@ -19030,7 +18853,7 @@
         <v>19</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>293</v>
@@ -19055,10 +18878,10 @@
         <v>20</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>289</v>
@@ -19080,7 +18903,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>67</v>
@@ -19105,7 +18928,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C27" s="10" t="s">
         <v>301</v>
@@ -19130,7 +18953,7 @@
         <v>23</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>77</v>
@@ -19155,7 +18978,7 @@
         <v>24</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C29" s="10" t="s">
         <v>310</v>
@@ -19180,16 +19003,16 @@
         <v>25</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F30" s="11" t="n">
         <v>46119</v>
@@ -19205,16 +19028,16 @@
         <v>26</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F31" s="11" t="n">
         <v>46055</v>
@@ -19230,16 +19053,16 @@
         <v>27</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F32" s="15" t="n">
         <v>45932</v>
@@ -19259,16 +19082,16 @@
         <v>28</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>46094</v>
@@ -19284,16 +19107,16 @@
         <v>29</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F34" s="15" t="n">
         <v>45931</v>
@@ -19313,13 +19136,13 @@
         <v>30</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C35" s="10" t="s">
         <v>51</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>43</v>
@@ -19338,13 +19161,13 @@
         <v>31</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>54</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>43</v>
@@ -19363,13 +19186,13 @@
         <v>32</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C37" s="10" t="s">
         <v>51</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>43</v>
@@ -19388,13 +19211,13 @@
         <v>33</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C38" s="10" t="s">
         <v>54</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>43</v>
@@ -19413,13 +19236,13 @@
         <v>34</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C39" s="10" t="s">
         <v>74</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>43</v>
@@ -19438,13 +19261,13 @@
         <v>35</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C40" s="14" t="s">
         <v>74</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E40" s="14" t="s">
         <v>43</v>
@@ -19467,13 +19290,13 @@
         <v>36</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C41" s="10" t="s">
         <v>51</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>43</v>
@@ -19492,13 +19315,13 @@
         <v>37</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C42" s="10" t="s">
         <v>74</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>43</v>
@@ -19517,13 +19340,13 @@
         <v>38</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C43" s="10" t="s">
         <v>42</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>43</v>
@@ -19542,13 +19365,13 @@
         <v>39</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C44" s="10" t="s">
         <v>51</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>43</v>
@@ -19567,13 +19390,13 @@
         <v>40</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>149</v>
@@ -19592,13 +19415,13 @@
         <v>41</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>90</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>63</v>
@@ -19617,13 +19440,13 @@
         <v>42</v>
       </c>
       <c r="B47" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="D47" s="10" t="s">
         <v>473</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>470</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>471</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>149</v>
@@ -19642,13 +19465,13 @@
         <v>43</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>149</v>
@@ -19667,13 +19490,13 @@
         <v>44</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>149</v>
@@ -19692,13 +19515,13 @@
         <v>45</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E50" s="10" t="s">
         <v>149</v>
@@ -19717,13 +19540,13 @@
         <v>46</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>149</v>
@@ -19742,13 +19565,13 @@
         <v>47</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>149</v>
@@ -19767,13 +19590,13 @@
         <v>48</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E53" s="18" t="s">
         <v>149</v>
@@ -19796,13 +19619,13 @@
         <v>49</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>149</v>
@@ -19821,13 +19644,13 @@
         <v>50</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>149</v>
@@ -19846,13 +19669,13 @@
         <v>51</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E56" s="10" t="s">
         <v>149</v>
@@ -19871,13 +19694,13 @@
         <v>52</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>149</v>
@@ -19896,13 +19719,13 @@
         <v>53</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E58" s="10" t="s">
         <v>149</v>
@@ -19919,7 +19742,7 @@
     <row r="59" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="21" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F60" s="22"/>
       <c r="G60" s="22"/>
@@ -19939,7 +19762,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F61" s="22"/>
       <c r="G61" s="22"/>
@@ -19950,83 +19773,26 @@
         <v>1</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>306</v>
+        <v>353</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>307</v>
+        <v>350</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F62" s="22"/>
       <c r="G62" s="22"/>
       <c r="H62" s="22"/>
     </row>
-    <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B63" s="18" t="s">
-        <v>516</v>
-      </c>
-      <c r="C63" s="18" t="s">
-        <v>306</v>
-      </c>
-      <c r="D63" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="E63" s="18" t="s">
-        <v>514</v>
-      </c>
-      <c r="F63" s="22"/>
-      <c r="G63" s="22"/>
-      <c r="H63" s="22"/>
-    </row>
-    <row r="64" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B64" s="18" t="s">
-        <v>517</v>
-      </c>
-      <c r="C64" s="18" t="s">
-        <v>306</v>
-      </c>
-      <c r="D64" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="E64" s="18" t="s">
-        <v>514</v>
-      </c>
-      <c r="F64" s="22"/>
-      <c r="G64" s="22"/>
-      <c r="H64" s="22"/>
-    </row>
-    <row r="65" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B65" s="18" t="s">
-        <v>520</v>
-      </c>
-      <c r="C65" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="D65" s="18" t="s">
-        <v>348</v>
-      </c>
-      <c r="E65" s="18" t="s">
-        <v>518</v>
-      </c>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
-      <c r="H65" s="22"/>
-    </row>
-    <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="67" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="64" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -20059,17 +19825,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F4" s="22"/>
       <c r="G4" s="22"/>
@@ -21691,7 +21457,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="21" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F68" s="22"/>
       <c r="G68" s="22"/>
@@ -21711,7 +21477,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F69" s="22"/>
       <c r="G69" s="22"/>
@@ -21731,7 +21497,7 @@
         <v>80</v>
       </c>
       <c r="E70" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F70" s="22"/>
       <c r="G70" s="22"/>
@@ -21751,7 +21517,7 @@
         <v>80</v>
       </c>
       <c r="E71" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F71" s="22"/>
       <c r="G71" s="22"/>
@@ -21771,7 +21537,7 @@
         <v>80</v>
       </c>
       <c r="E72" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F72" s="22"/>
       <c r="G72" s="22"/>
@@ -21791,7 +21557,7 @@
         <v>80</v>
       </c>
       <c r="E73" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F73" s="22"/>
       <c r="G73" s="22"/>
@@ -21811,7 +21577,7 @@
         <v>80</v>
       </c>
       <c r="E74" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F74" s="22"/>
       <c r="G74" s="22"/>
@@ -21831,7 +21597,7 @@
         <v>80</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F75" s="22"/>
       <c r="G75" s="22"/>
@@ -21851,7 +21617,7 @@
         <v>80</v>
       </c>
       <c r="E76" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F76" s="22"/>
       <c r="G76" s="22"/>
@@ -21871,7 +21637,7 @@
         <v>80</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F77" s="22"/>
       <c r="G77" s="22"/>
@@ -21891,7 +21657,7 @@
         <v>80</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F78" s="22"/>
       <c r="G78" s="22"/>
@@ -21911,7 +21677,7 @@
         <v>80</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F79" s="22"/>
       <c r="G79" s="22"/>
@@ -21931,7 +21697,7 @@
         <v>80</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F80" s="22"/>
       <c r="G80" s="22"/>
@@ -21951,7 +21717,7 @@
         <v>80</v>
       </c>
       <c r="E81" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F81" s="22"/>
       <c r="G81" s="22"/>
@@ -21971,7 +21737,7 @@
         <v>80</v>
       </c>
       <c r="E82" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F82" s="22"/>
       <c r="G82" s="22"/>
@@ -21991,7 +21757,7 @@
         <v>80</v>
       </c>
       <c r="E83" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F83" s="22"/>
       <c r="G83" s="22"/>
@@ -22011,7 +21777,7 @@
         <v>80</v>
       </c>
       <c r="E84" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F84" s="22"/>
       <c r="G84" s="22"/>
@@ -22031,7 +21797,7 @@
         <v>80</v>
       </c>
       <c r="E85" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F85" s="22"/>
       <c r="G85" s="22"/>
@@ -22051,7 +21817,7 @@
         <v>80</v>
       </c>
       <c r="E86" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F86" s="22"/>
       <c r="G86" s="22"/>
@@ -22090,17 +21856,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F4" s="22"/>
       <c r="G4" s="22"/>
@@ -22140,7 +21906,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>61</v>
@@ -22165,13 +21931,13 @@
         <v>2</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>67</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>63</v>
@@ -22190,13 +21956,13 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E8" s="18" t="s">
         <v>43</v>
@@ -22219,13 +21985,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E9" s="18" t="s">
         <v>43</v>
@@ -22248,13 +22014,13 @@
         <v>5</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>74</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>43</v>
@@ -22277,13 +22043,13 @@
         <v>6</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>43</v>
@@ -22302,13 +22068,13 @@
         <v>7</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>74</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E12" s="14" t="s">
         <v>43</v>
@@ -22331,13 +22097,13 @@
         <v>8</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>43</v>
@@ -22356,13 +22122,13 @@
         <v>9</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C14" s="18" t="s">
         <v>74</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E14" s="18" t="s">
         <v>43</v>
@@ -22385,13 +22151,13 @@
         <v>10</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>74</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>43</v>
@@ -22410,13 +22176,13 @@
         <v>11</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C16" s="18" t="s">
         <v>77</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E16" s="18" t="s">
         <v>40</v>
@@ -22439,13 +22205,13 @@
         <v>12</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>82</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>36</v>
@@ -22464,13 +22230,13 @@
         <v>13</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C18" s="14" t="s">
         <v>82</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E18" s="14" t="s">
         <v>36</v>
@@ -22493,13 +22259,13 @@
         <v>14</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>82</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E19" s="14" t="s">
         <v>36</v>
@@ -22522,13 +22288,13 @@
         <v>15</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>36</v>
@@ -22547,13 +22313,13 @@
         <v>16</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>82</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E21" s="18" t="s">
         <v>36</v>
@@ -22574,7 +22340,7 @@
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F23" s="22"/>
       <c r="G23" s="22"/>
@@ -22594,7 +22360,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F24" s="22"/>
       <c r="G24" s="22"/>
@@ -22605,16 +22371,16 @@
         <v>1</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C25" s="18" t="s">
         <v>82</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F25" s="22"/>
       <c r="G25" s="22"/>
@@ -22625,16 +22391,16 @@
         <v>2</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C26" s="18" t="s">
         <v>82</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F26" s="22"/>
       <c r="G26" s="22"/>
@@ -22645,16 +22411,16 @@
         <v>3</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C27" s="18" t="s">
         <v>82</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F27" s="22"/>
       <c r="G27" s="22"/>
@@ -22665,16 +22431,16 @@
         <v>4</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C28" s="18" t="s">
         <v>34</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F28" s="22"/>
       <c r="G28" s="22"/>
@@ -22685,16 +22451,16 @@
         <v>5</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>82</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F29" s="22"/>
       <c r="G29" s="22"/>
@@ -22734,17 +22500,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F4" s="22"/>
       <c r="G4" s="22"/>
@@ -23155,7 +22921,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F21" s="22"/>
       <c r="G21" s="22"/>
@@ -23175,7 +22941,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F22" s="22"/>
       <c r="G22" s="22"/>
@@ -23195,7 +22961,7 @@
         <v>143</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F23" s="22"/>
       <c r="G23" s="22"/>
@@ -23215,7 +22981,7 @@
         <v>143</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F24" s="22"/>
       <c r="G24" s="22"/>
@@ -23235,7 +23001,7 @@
         <v>143</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F25" s="22"/>
       <c r="G25" s="22"/>
@@ -23255,7 +23021,7 @@
         <v>143</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F26" s="22"/>
       <c r="G26" s="22"/>
@@ -23275,7 +23041,7 @@
         <v>143</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F27" s="22"/>
       <c r="G27" s="22"/>
@@ -23295,7 +23061,7 @@
         <v>143</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F28" s="22"/>
       <c r="G28" s="22"/>
@@ -23334,17 +23100,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F4" s="22"/>
       <c r="G4" s="22"/>
@@ -23635,7 +23401,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F17" s="22"/>
       <c r="G17" s="22"/>
@@ -23655,7 +23421,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F18" s="22"/>
       <c r="G18" s="22"/>
@@ -23675,7 +23441,7 @@
         <v>35</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F19" s="22"/>
       <c r="G19" s="22"/>
@@ -23695,7 +23461,7 @@
         <v>35</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F20" s="22"/>
       <c r="G20" s="22"/>

--- a/МО 19.10.2026/Списки МО итог (ред. 19.10.2026).xlsx
+++ b/МО 19.10.2026/Списки МО итог (ред. 19.10.2026).xlsx
@@ -989,7 +989,7 @@
     <t xml:space="preserve">Каменев Дмитрий Викторович</t>
   </si>
   <si>
-    <t xml:space="preserve">п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.18.1, п.18.2</t>
+    <t xml:space="preserve">п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.18.1</t>
   </si>
   <si>
     <t xml:space="preserve">Карпачева Татьяна Владимировна</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">Нестеров Аркадий Николаевич</t>
   </si>
   <si>
-    <t xml:space="preserve">п.4.4, п.5.1, п.6.2, п.18.1, п.18.2</t>
+    <t xml:space="preserve">п.4.4, п.5.1, п.6.2, п.18.1</t>
   </si>
   <si>
     <t xml:space="preserve">Ноженко Екатерина Сергеевна</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">п.1 Прил.№2: управление транспортными средствами.</t>
   </si>
   <si>
-    <t xml:space="preserve">п.1 Прил.№2: управление транспортными средствами (погрузчик; п.18.1, п.18.2 приложения к Приказу №29н).</t>
+    <t xml:space="preserve">п.1 Прил.№2: управление транспортными средствами (погрузчик; п.18.1 приложения к Приказу №29н).</t>
   </si>
   <si>
     <t xml:space="preserve">п.11 Прил.№2: обслуживание электроустановок предприятия.</t>
